--- a/results/feature_selection/global/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/rP/metrics_global.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
@@ -483,43 +488,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>T, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9588636422156351</v>
+        <v>0.4891559595012183</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01249817285818899</v>
+        <v>0.03316013582864672</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007692429433925238</v>
+        <v>0.009552697285153684</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02773522928321531</v>
+        <v>0.09773790096556036</v>
       </c>
       <c r="H2" t="n">
-        <v>146.7697458838751</v>
+        <v>240.2748335495067</v>
       </c>
       <c r="I2" t="n">
-        <v>-859.0928609284084</v>
+        <v>0.1619401002492421</v>
       </c>
       <c r="J2" t="n">
-        <v>-816.7886374443328</v>
+        <v>-568.7155340403283</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-557.4344077779082</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -527,35 +535,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9582967209818677</v>
+        <v>0.4749922869511376</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01262902807208773</v>
+        <v>0.0406364434171453</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007798442747213947</v>
+        <v>0.009817555569856104</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02792569201866616</v>
+        <v>0.09908357870937093</v>
       </c>
       <c r="H3" t="n">
-        <v>150.0899322942217</v>
+        <v>242.7537649678916</v>
       </c>
       <c r="I3" t="n">
-        <v>-857.3956219447432</v>
+        <v>0.165874602813558</v>
       </c>
       <c r="J3" t="n">
-        <v>-815.0913984606676</v>
+        <v>-567.3243057940455</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-558.8634610972304</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -563,29 +574,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9566897587142807</v>
+        <v>0.4511937946035434</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01297736341407486</v>
+        <v>0.03486327419164327</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000809894197738865</v>
+        <v>0.01026258335762797</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02845864012455383</v>
+        <v>0.1013044093691285</v>
       </c>
       <c r="H4" t="n">
-        <v>167.8845066468766</v>
+        <v>359.526635618329</v>
       </c>
       <c r="I4" t="n">
-        <v>-852.7072604241964</v>
+        <v>0.1733256699692766</v>
       </c>
       <c r="J4" t="n">
-        <v>-810.4030369401208</v>
+        <v>-561.827084529636</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-553.3662398328208</v>
       </c>
     </row>
     <row r="5">
@@ -595,141 +609,153 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9558102831781984</v>
+        <v>0.2890731896821619</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01704831613642215</v>
+        <v>0.06438907382615268</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008263402417363448</v>
+        <v>0.01329421129046601</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02874613437901425</v>
+        <v>0.1153005259765367</v>
       </c>
       <c r="H5" t="n">
-        <v>170.0762793428653</v>
+        <v>1056.648574267707</v>
       </c>
       <c r="I5" t="n">
-        <v>-850.2144903359182</v>
+        <v>0.2250839909986777</v>
       </c>
       <c r="J5" t="n">
-        <v>-807.9102668518426</v>
+        <v>-525.7328958974034</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-511.6314880693782</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>X, V, P, dXdt, dVdt, Xlag1, Plag1, X_calc</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9484634206789998</v>
+        <v>0.2454902225319104</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01825134018767791</v>
+        <v>0.0590281192138337</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009637253297212533</v>
+        <v>0.01410920541581324</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03104392581039411</v>
+        <v>0.1187821763389324</v>
       </c>
       <c r="H6" t="n">
-        <v>205.4526984162749</v>
+        <v>405.285690335662</v>
       </c>
       <c r="I6" t="n">
-        <v>-845.143324721919</v>
+        <v>0.2377293770314962</v>
       </c>
       <c r="J6" t="n">
-        <v>-822.5810721970787</v>
+        <v>-522.3550507033493</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-513.8942060065342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, T, Plag1, dXdt_calc</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9060161098201892</v>
+        <v>0.24546930724169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01806952710993599</v>
+        <v>0.05899378001235211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001757482874210023</v>
+        <v>0.01410959652820815</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0419223433768918</v>
+        <v>0.1187838226704636</v>
       </c>
       <c r="H7" t="n">
-        <v>231.9827601539223</v>
+        <v>405.9803718237305</v>
       </c>
       <c r="I7" t="n">
-        <v>-778.6402121626318</v>
+        <v>0.2377359253972387</v>
       </c>
       <c r="J7" t="n">
-        <v>-767.3590859002117</v>
+        <v>-522.3516134251071</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-513.890768728292</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7575828232643851</v>
+        <v>0.2451592745258487</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02557708549984367</v>
+        <v>0.05885323758270045</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004533160265148386</v>
+        <v>0.01411539408763556</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0673287476873615</v>
+        <v>0.1188082239899055</v>
       </c>
       <c r="H8" t="n">
-        <v>779.916006324203</v>
+        <v>409.1565794231239</v>
       </c>
       <c r="I8" t="n">
-        <v>-667.1456581028696</v>
+        <v>0.2378329935035903</v>
       </c>
       <c r="J8" t="n">
-        <v>-664.3253765372646</v>
+        <v>-522.3006729384374</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-513.8398282416223</v>
       </c>
     </row>
     <row r="9">
@@ -739,33 +765,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7238509536446905</v>
+        <v>0.02375486944341754</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02795435421025236</v>
+        <v>0.04311235806185047</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005163940530343595</v>
+        <v>0.0182556190715405</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07186056310900713</v>
+        <v>0.1351133563773045</v>
       </c>
       <c r="H9" t="n">
-        <v>693.3560878493167</v>
+        <v>860.5423187003753</v>
       </c>
       <c r="I9" t="n">
-        <v>-618.990859960733</v>
+        <v>0.3081524725170531</v>
       </c>
       <c r="J9" t="n">
-        <v>-571.0460733454474</v>
+        <v>-486.4070116495354</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-472.3056038215103</v>
       </c>
     </row>
     <row r="10">
@@ -775,33 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P, T, mu_calc</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7108090138241647</v>
+        <v>-0.002812996318679151</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03635463250997176</v>
+        <v>0.05549673832557939</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005407822602443388</v>
+        <v>0.01875243367446728</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07353789908913219</v>
+        <v>0.1369395256106405</v>
       </c>
       <c r="H10" t="n">
-        <v>1555.802635231062</v>
+        <v>2001.010820244024</v>
       </c>
       <c r="I10" t="n">
-        <v>-617.2686842041836</v>
+        <v>0.6289412049354618</v>
       </c>
       <c r="J10" t="n">
-        <v>-574.964460720108</v>
+        <v>-491.0775356380952</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-488.2572540724902</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/rP/metrics_global.xlsx
@@ -500,28 +500,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4891559595012183</v>
+        <v>0.4853863452917612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03316013582864672</v>
+        <v>0.03378523857969958</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009552697285153684</v>
+        <v>0.009477468343804082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09773790096556036</v>
+        <v>0.0973522898744764</v>
       </c>
       <c r="H2" t="n">
-        <v>240.2748335495067</v>
+        <v>235.2202569476866</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1619401002492421</v>
+        <v>0.1630183242531345</v>
       </c>
       <c r="J2" t="n">
-        <v>-568.7155340403283</v>
+        <v>-579.0135943908931</v>
       </c>
       <c r="K2" t="n">
-        <v>-557.4344077779082</v>
+        <v>-567.6684667630872</v>
       </c>
     </row>
     <row r="3">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4749922869511376</v>
+        <v>0.4684984091972254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0406364434171453</v>
+        <v>0.04002324778623471</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009817555569856104</v>
+        <v>0.009788487840204526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09908357870937093</v>
+        <v>0.09893678709259021</v>
       </c>
       <c r="H3" t="n">
-        <v>242.7537649678916</v>
+        <v>234.0002806144358</v>
       </c>
       <c r="I3" t="n">
-        <v>0.165874602813558</v>
+        <v>0.1678024187289756</v>
       </c>
       <c r="J3" t="n">
-        <v>-567.3243057940455</v>
+        <v>-576.9450850442081</v>
       </c>
       <c r="K3" t="n">
-        <v>-558.8634610972304</v>
+        <v>-568.4362393233537</v>
       </c>
     </row>
     <row r="4">
@@ -570,36 +570,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I, V_calc, Xlag1_calc</t>
+          <t>I, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4511937946035434</v>
+        <v>0.4303068181145793</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03486327419164327</v>
+        <v>0.0358648239502855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01026258335762797</v>
+        <v>0.01049184965770333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1013044093691285</v>
+        <v>0.1024297303408699</v>
       </c>
       <c r="H4" t="n">
-        <v>359.526635618329</v>
+        <v>369.9818912687821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1733256699692766</v>
+        <v>0.1802522493260186</v>
       </c>
       <c r="J4" t="n">
-        <v>-561.827084529636</v>
+        <v>-566.2017248352681</v>
       </c>
       <c r="K4" t="n">
-        <v>-553.3662398328208</v>
+        <v>-554.8565972074622</v>
       </c>
     </row>
     <row r="5">
@@ -617,28 +617,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2890731896821619</v>
+        <v>0.2893903447895624</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06438907382615268</v>
+        <v>0.06355803193776786</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01329421129046601</v>
+        <v>0.01308706143033992</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1153005259765367</v>
+        <v>0.1143986950552318</v>
       </c>
       <c r="H5" t="n">
-        <v>1056.648574267707</v>
+        <v>1018.438158986416</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2250839909986777</v>
+        <v>0.2248438395643693</v>
       </c>
       <c r="J5" t="n">
-        <v>-525.7328958974034</v>
+        <v>-536.3525329542628</v>
       </c>
       <c r="K5" t="n">
-        <v>-511.6314880693782</v>
+        <v>-522.1711234195054</v>
       </c>
     </row>
     <row r="6">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2454902225319104</v>
+        <v>0.2426748872677899</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0590281192138337</v>
+        <v>0.05877730171741251</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01410920541581324</v>
+        <v>0.01394740445812051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1187821763389324</v>
+        <v>0.1180991297940866</v>
       </c>
       <c r="H6" t="n">
-        <v>405.285690335662</v>
+        <v>432.546906178768</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2377293770314962</v>
+        <v>0.2384607169403474</v>
       </c>
       <c r="J6" t="n">
-        <v>-522.3550507033493</v>
+        <v>-532.3301928953659</v>
       </c>
       <c r="K6" t="n">
-        <v>-513.8942060065342</v>
+        <v>-523.8213471745115</v>
       </c>
     </row>
     <row r="7">
@@ -695,28 +695,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.24546930724169</v>
+        <v>0.2426412897601681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05899378001235211</v>
+        <v>0.05874138474074486</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01410959652820815</v>
+        <v>0.01394802321223246</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1187838226704636</v>
+        <v>0.1181017494037767</v>
       </c>
       <c r="H7" t="n">
-        <v>405.9803718237305</v>
+        <v>433.1868743946573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2377359253972387</v>
+        <v>0.2384712293205123</v>
       </c>
       <c r="J7" t="n">
-        <v>-522.3516134251071</v>
+        <v>-532.324603232498</v>
       </c>
       <c r="K7" t="n">
-        <v>-513.890768728292</v>
+        <v>-523.8157575116436</v>
       </c>
     </row>
     <row r="8">
@@ -734,28 +734,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2451592745258487</v>
+        <v>0.2422657386376721</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05885323758270045</v>
+        <v>0.05859606593784469</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01411539408763556</v>
+        <v>0.01395493961221985</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1188082239899055</v>
+        <v>0.1181310273053606</v>
       </c>
       <c r="H8" t="n">
-        <v>409.1565794231239</v>
+        <v>436.1679467762493</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2378329935035903</v>
+        <v>0.2385887361372523</v>
       </c>
       <c r="J8" t="n">
-        <v>-522.3006729384374</v>
+        <v>-532.2621391549918</v>
       </c>
       <c r="K8" t="n">
-        <v>-513.8398282416223</v>
+        <v>-523.7532934341374</v>
       </c>
     </row>
     <row r="9">
@@ -773,28 +773,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02375486944341754</v>
+        <v>0.03697335939637836</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04311235806185047</v>
+        <v>0.04331740399180194</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0182556190715405</v>
+        <v>0.01773574101086652</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1351133563773045</v>
+        <v>0.1331756021607056</v>
       </c>
       <c r="H9" t="n">
-        <v>860.5423187003753</v>
+        <v>989.9096233128965</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3081524725170531</v>
+        <v>0.3038230108886931</v>
       </c>
       <c r="J9" t="n">
-        <v>-486.4070116495354</v>
+        <v>-498.053849562888</v>
       </c>
       <c r="K9" t="n">
-        <v>-472.3056038215103</v>
+        <v>-483.8724400281307</v>
       </c>
     </row>
     <row r="10">
@@ -812,28 +812,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.002812996318679151</v>
+        <v>-0.0003382870853743114</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05549673832557939</v>
+        <v>0.05505635803275964</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01875243367446728</v>
+        <v>0.01842289718161855</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1369395256106405</v>
+        <v>0.1357309735529019</v>
       </c>
       <c r="H10" t="n">
-        <v>2001.010820244024</v>
+        <v>1901.901301005283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6289412049354618</v>
+        <v>0.6269950283054906</v>
       </c>
       <c r="J10" t="n">
-        <v>-491.0775356380952</v>
+        <v>-501.2642829711652</v>
       </c>
       <c r="K10" t="n">
-        <v>-488.2572540724902</v>
+        <v>-498.4280010642137</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/rP/metrics_global.xlsx
@@ -488,163 +488,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4853863452917612</v>
+        <v>0.9582967209818677</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03378523857969958</v>
+        <v>0.01262902807208773</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009477468343804082</v>
+        <v>0.0007798442747213947</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0973522898744764</v>
+        <v>0.02792569201866616</v>
       </c>
       <c r="H2" t="n">
-        <v>235.2202569476866</v>
+        <v>150.0899322942217</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1630183242531345</v>
+        <v>0.01455687469774467</v>
       </c>
       <c r="J2" t="n">
-        <v>-579.0135943908931</v>
+        <v>-881.3956219447432</v>
       </c>
       <c r="K2" t="n">
-        <v>-567.6684667630872</v>
+        <v>-872.9347772479281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1, X_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4684984091972254</v>
+        <v>0.9578922059522963</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04002324778623471</v>
+        <v>0.01316993109460203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009788487840204526</v>
+        <v>0.0007874086374592233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09893678709259021</v>
+        <v>0.02806080250918037</v>
       </c>
       <c r="H3" t="n">
-        <v>234.0002806144358</v>
+        <v>153.1579899618126</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1678024187289756</v>
+        <v>0.01568352426053257</v>
       </c>
       <c r="J3" t="n">
-        <v>-576.9450850442081</v>
+        <v>-876.1986380300366</v>
       </c>
       <c r="K3" t="n">
-        <v>-568.4362393233537</v>
+        <v>-862.0972302020114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1, X_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4303068181145793</v>
+        <v>0.9578257877463514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0358648239502855</v>
+        <v>0.01526728096002243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01049184965770333</v>
+        <v>0.0007886506466935781</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1024297303408699</v>
+        <v>0.02808292446832377</v>
       </c>
       <c r="H4" t="n">
-        <v>369.9818912687821</v>
+        <v>166.3286660324466</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1802522493260186</v>
+        <v>0.01620431912878008</v>
       </c>
       <c r="J4" t="n">
-        <v>-566.2017248352681</v>
+        <v>-874.0032022637689</v>
       </c>
       <c r="K4" t="n">
-        <v>-554.8565972074622</v>
+        <v>-857.0815128701387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2893903447895624</v>
+        <v>0.9566897587142807</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06355803193776786</v>
+        <v>0.01297736341407486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01308706143033992</v>
+        <v>0.000809894197738865</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1143986950552318</v>
+        <v>0.02845864012455383</v>
       </c>
       <c r="H5" t="n">
-        <v>1018.438158986416</v>
+        <v>167.8845066468766</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2248438395643693</v>
+        <v>0.01505999832413298</v>
       </c>
       <c r="J5" t="n">
-        <v>-536.3525329542628</v>
+        <v>-876.7072604241964</v>
       </c>
       <c r="K5" t="n">
-        <v>-522.1711234195054</v>
+        <v>-868.2464157273813</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,110 +652,110 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2426748872677899</v>
+        <v>0.9053681133960535</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05877730171741251</v>
+        <v>0.02001313117880163</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01394740445812051</v>
+        <v>0.00176960029790667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1180991297940866</v>
+        <v>0.04206661738132352</v>
       </c>
       <c r="H6" t="n">
-        <v>432.546906178768</v>
+        <v>224.46999923786</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2384607169403474</v>
+        <v>0.03112828618971863</v>
       </c>
       <c r="J6" t="n">
-        <v>-532.3301928953659</v>
+        <v>-779.7881957078824</v>
       </c>
       <c r="K6" t="n">
-        <v>-523.8213471745115</v>
+        <v>-771.3273510110673</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P, I, Plag1, X_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2426412897601681</v>
+        <v>0.9042764135936864</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05874138474074486</v>
+        <v>0.02047732538573871</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01394802321223246</v>
+        <v>0.001790014899842894</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1181017494037767</v>
+        <v>0.04230856768838782</v>
       </c>
       <c r="H7" t="n">
-        <v>433.1868743946573</v>
+        <v>340.5230452852427</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2384712293205123</v>
+        <v>0.03197008635178412</v>
       </c>
       <c r="J7" t="n">
-        <v>-532.324603232498</v>
+        <v>-776.3658855684629</v>
       </c>
       <c r="K7" t="n">
-        <v>-523.8157575116436</v>
+        <v>-765.0847593060428</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2422657386376721</v>
+        <v>0.7575828232643851</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05859606593784469</v>
+        <v>0.02557708549984367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01395493961221985</v>
+        <v>0.004533160265148386</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1181310273053606</v>
+        <v>0.0673287476873615</v>
       </c>
       <c r="H8" t="n">
-        <v>436.1679467762493</v>
+        <v>779.916006324203</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2385887361372523</v>
+        <v>0.07639836520628836</v>
       </c>
       <c r="J8" t="n">
-        <v>-532.2621391549918</v>
+        <v>-667.1456581028696</v>
       </c>
       <c r="K8" t="n">
-        <v>-523.7532934341374</v>
+        <v>-664.3253765372646</v>
       </c>
     </row>
     <row r="9">
@@ -765,36 +765,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.03697335939637836</v>
+        <v>0.7193542586567984</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04331740399180194</v>
+        <v>0.02786454037957408</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01773574101086652</v>
+        <v>0.005248027967208004</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1331756021607056</v>
+        <v>0.07244327413368341</v>
       </c>
       <c r="H9" t="n">
-        <v>989.9096233128965</v>
+        <v>678.9470635939495</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3038230108886931</v>
+        <v>0.08836734198000611</v>
       </c>
       <c r="J9" t="n">
-        <v>-498.053849562888</v>
+        <v>-648.987959381409</v>
       </c>
       <c r="K9" t="n">
-        <v>-483.8724400281307</v>
+        <v>-646.167677815804</v>
       </c>
     </row>
     <row r="10">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>P, T, mu_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.0003382870853743114</v>
+        <v>0.7107982330491003</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05505635803275964</v>
+        <v>0.03640278374344891</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01842289718161855</v>
+        <v>0.00540802420111642</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1357309735529019</v>
+        <v>0.07353926978911621</v>
       </c>
       <c r="H10" t="n">
-        <v>1901.901301005283</v>
+        <v>1554.929370078434</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6269950283054906</v>
+        <v>0.09204614702605143</v>
       </c>
       <c r="J10" t="n">
-        <v>-501.2642829711652</v>
+        <v>-641.2640616839293</v>
       </c>
       <c r="K10" t="n">
-        <v>-498.4280010642137</v>
+        <v>-632.8032169871142</v>
       </c>
     </row>
   </sheetData>
